--- a/sampleData/Direct.xlsx
+++ b/sampleData/Direct.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijaytomar/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijaytomar/AZOnline_Automation/AZOnline/sampleData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{874D5089-A57F-E84C-92C8-AD13E0DAA5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0795CEFD-2FA1-9E4C-A8E0-7909C0EED8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1480" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master_Template" sheetId="1" r:id="rId1"/>
@@ -13472,9 +13472,11 @@
   <dimension ref="A1:E893"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="5" width="18" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">

--- a/sampleData/Direct.xlsx
+++ b/sampleData/Direct.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijaytomar/AZOnline_Automation/AZOnline/sampleData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0795CEFD-2FA1-9E4C-A8E0-7909C0EED8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB55687-9CA8-1F4B-B4DB-55025EF75333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master_Template" sheetId="1" r:id="rId1"/>
-    <sheet name="FlowNB" sheetId="2" r:id="rId2"/>
-    <sheet name="Conventions" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="FlowNB" sheetId="2" r:id="rId3"/>
+    <sheet name="Conventions" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6296" uniqueCount="1093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6388" uniqueCount="1146">
   <si>
     <t>Section</t>
   </si>
@@ -3301,6 +3302,165 @@
   </si>
   <si>
     <t>Use Conviction1/Conviction2/Conviction3 fields</t>
+  </si>
+  <si>
+    <t>ScenarioId</t>
+  </si>
+  <si>
+    <t>ScenarioName</t>
+  </si>
+  <si>
+    <t>Journey</t>
+  </si>
+  <si>
+    <t>StartFrom</t>
+  </si>
+  <si>
+    <t>PolicyNumber</t>
+  </si>
+  <si>
+    <t>Execute</t>
+  </si>
+  <si>
+    <t>Step1Action</t>
+  </si>
+  <si>
+    <t>Step1SubType</t>
+  </si>
+  <si>
+    <t>Step1Portal</t>
+  </si>
+  <si>
+    <t>Step1Data</t>
+  </si>
+  <si>
+    <t>Step2Action</t>
+  </si>
+  <si>
+    <t>Step2SubType</t>
+  </si>
+  <si>
+    <t>Step2Portal</t>
+  </si>
+  <si>
+    <t>Step2Data</t>
+  </si>
+  <si>
+    <t>Step3Action</t>
+  </si>
+  <si>
+    <t>Step3SubType</t>
+  </si>
+  <si>
+    <t>Step3Portal</t>
+  </si>
+  <si>
+    <t>Step3Data</t>
+  </si>
+  <si>
+    <t>SC001</t>
+  </si>
+  <si>
+    <t>NB Direct Only</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>NewBusiness</t>
+  </si>
+  <si>
+    <t>Simple new business</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>SC002</t>
+  </si>
+  <si>
+    <t>NB then MTA Replace Car</t>
+  </si>
+  <si>
+    <t>NB + Replace Car</t>
+  </si>
+  <si>
+    <t>MTA</t>
+  </si>
+  <si>
+    <t>ReplaceCar</t>
+  </si>
+  <si>
+    <t>CustomerPortal</t>
+  </si>
+  <si>
+    <t>MTA_RC_01</t>
+  </si>
+  <si>
+    <t>SC003</t>
+  </si>
+  <si>
+    <t>NB → MTA → Renewal</t>
+  </si>
+  <si>
+    <t>Full lifecycle</t>
+  </si>
+  <si>
+    <t>AddDriver</t>
+  </si>
+  <si>
+    <t>MTA_AD_01</t>
+  </si>
+  <si>
+    <t>Renewal</t>
+  </si>
+  <si>
+    <t>SupportPortal</t>
+  </si>
+  <si>
+    <t>REN_STD_01</t>
+  </si>
+  <si>
+    <t>SC004</t>
+  </si>
+  <si>
+    <t>Existing Policy MTA Only</t>
+  </si>
+  <si>
+    <t>ExistingPolicy</t>
+  </si>
+  <si>
+    <t>P12345678</t>
+  </si>
+  <si>
+    <t>Replace car only</t>
+  </si>
+  <si>
+    <t>MTA_RC_02</t>
+  </si>
+  <si>
+    <t>SC005</t>
+  </si>
+  <si>
+    <t>Existing Policy Renewal Only</t>
+  </si>
+  <si>
+    <t>P87654321</t>
+  </si>
+  <si>
+    <t>Renewal only</t>
+  </si>
+  <si>
+    <t>REN_STD_02</t>
+  </si>
+  <si>
+    <t>SC006</t>
+  </si>
+  <si>
+    <t>NB minimal (fallback mapping)</t>
+  </si>
+  <si>
+    <t>No subtype</t>
   </si>
 </sst>
 </file>
@@ -13468,6 +13628,326 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A678BB0-76B1-3749-896D-B16977334517}">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I2" t="s">
+        <v>981</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K2" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>981</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K3" t="s">
+        <v>940</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="N3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O3" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I4" t="s">
+        <v>981</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K4" t="s">
+        <v>941</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="P4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>981</v>
+      </c>
+      <c r="R4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="S4" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I6" t="s">
+        <v>981</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K7" t="s">
+        <v>939</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E893"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -28665,7 +29145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/sampleData/Direct.xlsx
+++ b/sampleData/Direct.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijaytomar/AZOnline_Automation/AZOnline/sampleData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB55687-9CA8-1F4B-B4DB-55025EF75333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09534084-A383-7C43-825A-96A752B73F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master_Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="E2E Execution" sheetId="4" r:id="rId2"/>
     <sheet name="FlowNB" sheetId="2" r:id="rId3"/>
     <sheet name="Conventions" sheetId="3" r:id="rId4"/>
   </sheets>
